--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NORTH_CAROLINA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NORTH_CAROLINA_2015.xlsx
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C204">
@@ -6511,7 +6511,7 @@
         <v>389</v>
       </c>
       <c r="D342">
-        <v>0.009593094944512947</v>
+        <v>0.009593094944512949</v>
       </c>
     </row>
     <row r="343">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C348">
@@ -9607,7 +9607,7 @@
         <v>39</v>
       </c>
       <c r="D514">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="515">
@@ -9751,7 +9751,7 @@
         <v>39</v>
       </c>
       <c r="D522">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="523">
@@ -15403,7 +15403,7 @@
         <v>39</v>
       </c>
       <c r="D836">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="837">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C958">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C959">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1030">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1031">
@@ -22063,7 +22063,7 @@
         <v>39</v>
       </c>
       <c r="D1206">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="1207">
@@ -22279,7 +22279,7 @@
         <v>39</v>
       </c>
       <c r="D1218">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="1219">
@@ -25249,7 +25249,7 @@
         <v>39</v>
       </c>
       <c r="D1383">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="1384">
@@ -25807,7 +25807,7 @@
         <v>39</v>
       </c>
       <c r="D1414">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="1415">
@@ -30199,7 +30199,7 @@
         <v>39</v>
       </c>
       <c r="D1658">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="1659">
@@ -30811,7 +30811,7 @@
         <v>39</v>
       </c>
       <c r="D1692">
-        <v>0.0009617755856966707</v>
+        <v>0.0009617755856966709</v>
       </c>
     </row>
     <row r="1693">
